--- a/reporty/ukazky/F__CZ051__2026-10-15/priloha.xlsx
+++ b/reporty/ukazky/F__CZ051__2026-10-15/priloha.xlsx
@@ -12569,7 +12569,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-19T10:09:05+00:00</t>
+          <t>2026-10-19T10:22:30+00:00</t>
         </is>
       </c>
     </row>

--- a/reporty/ukazky/F__CZ051__2026-10-15/priloha.xlsx
+++ b/reporty/ukazky/F__CZ051__2026-10-15/priloha.xlsx
@@ -33,11 +33,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T21_mzdy_aktualni" sheetId="24" state="visible" r:id="rId24"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T10_zaniky_po" sheetId="25" state="visible" r:id="rId25"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T18_mira_zaniku_po" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T11_dynamika_csu" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T12_demografie_cr" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T19_zjisteni" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metodika" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zdroj a licence" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T29_zaniky_zpusob" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T30_mira_zaniku_ostatni" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T11_dynamika_csu" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T12_demografie_cr" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T19_zjisteni" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metodika" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zdroj a licence" sheetId="33" state="visible" r:id="rId33"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -450,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -937,34 +939,58 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>T11_dynamika_csu</t>
+          <t>T29_zaniky_zpusob</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Vznik a zánik ekonomických subjektů v území – všechny obory (ČSÚ, RES05)</t>
+          <t>Zaniklé právnické osoby v oboru podle způsobu zániku (RES, 2023–2026)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>T12_demografie_cr</t>
+          <t>T30_mira_zaniku_ostatni</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Demografie podniků v ČR – kontext (ČSÚ, RESDP00; jednotka podnik)</t>
+          <t>Míra zániku právnických osob – obor a všechny ostatní obory, celkem a bez kódu 04 (RES)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>T11_dynamika_csu</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Vznik a zánik ekonomických subjektů v území – všechny obory (ČSÚ, RES05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>T12_demografie_cr</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Demografie podniků v ČR – kontext (ČSÚ, RESDP00; jednotka podnik)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>T19_zjisteni</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>Zjištění detektoru (seřazeno podle síly)</t>
         </is>
@@ -6185,226 +6211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Vznik a zánik ekonomických subjektů v území – všechny obory (ČSÚ, RES05)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Zdroj: Český statistický úřad, Registr ekonomických subjektů (RES) – otevřená data, stav k 15. 10. 2026; licence CC BY 4.0 (https://csu.gov.cz/podminky_pro_vyuzivani_a_dalsi_zverejnovani_statistickych_udaju_csu); vlastní výpočet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Odvozené údaje, nejde o oficiální statistiku ČSÚ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Položka</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>FO</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>PO</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Celkem</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Poznámka</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2023 – vzniklé</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2859</v>
-      </c>
-      <c r="C6" t="n">
-        <v>785</v>
-      </c>
-      <c r="D6" t="n">
-        <v>3644</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2023 – zaniklé</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>13252</v>
-      </c>
-      <c r="C7" t="n">
-        <v>483</v>
-      </c>
-      <c r="D7" t="n">
-        <v>13735</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>mimořádný výkyv: hromadný zánik FO v 1. čtvrtletí 2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2024 – vzniklé</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>3326</v>
-      </c>
-      <c r="C8" t="n">
-        <v>768</v>
-      </c>
-      <c r="D8" t="n">
-        <v>4094</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2024 – zaniklé</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>3390</v>
-      </c>
-      <c r="C9" t="n">
-        <v>582</v>
-      </c>
-      <c r="D9" t="n">
-        <v>3972</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2025 – vzniklé</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>3239</v>
-      </c>
-      <c r="C10" t="n">
-        <v>766</v>
-      </c>
-      <c r="D10" t="n">
-        <v>4005</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2025 – zaniklé</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2003</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1221</v>
-      </c>
-      <c r="D11" t="n">
-        <v>3224</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026 – vzniklé</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1880</v>
-      </c>
-      <c r="C12" t="n">
-        <v>425</v>
-      </c>
-      <c r="D12" t="n">
-        <v>2305</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2 čtvrtletí</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026 – zaniklé</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>850</v>
-      </c>
-      <c r="C13" t="n">
-        <v>516</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1366</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2 čtvrtletí</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>ČSÚ nepublikuje vznik a zánik v členění podle oboru (kraj × sekce); jde o celé území. Čísla FO a PO pod prahem se nezveřejňují (zůstává jen celkem).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -6420,7 +6227,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demografie podniků v ČR – kontext (ČSÚ, RESDP00; jednotka podnik)</t>
+          <t>Zaniklé právnické osoby v oboru podle způsobu zániku (RES, 2023–2026)</t>
         </is>
       </c>
     </row>
@@ -6446,32 +6253,32 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Stavebnictví: aktivní podniky</t>
+          <t>Zaniklé PO celkem</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Stavebnictví: míra vzniků (%)</t>
+          <t>Zrušení bez likvidace bez nástupců (04)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Stavebnictví: míra zániků (%)</t>
+          <t>Ostatní způsoby celkem</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Všechna odvětví: aktivní podniky</t>
+          <t>z toho likvidace (01)</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Všechna odvětví: míra vzniků (%)</t>
+          <t>z toho jiný způsob</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Všechna odvětví: míra zániků (%)</t>
+          <t>Podíl kódu 04 (%)</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -6483,267 +6290,677 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2019 – podniky FO</t>
+          <t>Liberecký kraj – 2023</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>151021</v>
+        <v>35</v>
       </c>
       <c r="C6" t="n">
-        <v>7.81</v>
+        <v>25</v>
       </c>
       <c r="D6" t="n">
-        <v>7.44</v>
-      </c>
-      <c r="E6" t="n">
-        <v>903037</v>
-      </c>
-      <c r="F6" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>7.84</v>
+        <v>71.40000000000001</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>likvidace a jiný způsob jen společně (pod prahem)</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2019 – podniky PO</t>
+          <t>Liberecký kraj – 2024</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32611</v>
-      </c>
-      <c r="C7" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="D7" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="E7" t="n">
-        <v>306300</v>
-      </c>
-      <c r="F7" t="n">
-        <v>8.26</v>
-      </c>
-      <c r="G7" t="n">
-        <v>3.73</v>
+        <v>49</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>aspoň 81 %</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>způsoby jen jako pásmo podílu (pod prahem)</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2020 – podniky FO</t>
+          <t>Liberecký kraj – 2025</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>151683</v>
-      </c>
-      <c r="C8" t="n">
-        <v>7.42</v>
-      </c>
-      <c r="D8" t="n">
-        <v>6.89</v>
-      </c>
-      <c r="E8" t="n">
-        <v>906249</v>
-      </c>
-      <c r="F8" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="G8" t="n">
-        <v>7.69</v>
+        <v>103</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>aspoň 91 %</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>způsoby jen jako pásmo podílu (pod prahem)</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2020 – podniky PO</t>
+          <t>Liberecký kraj – 2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34021</v>
-      </c>
-      <c r="C9" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="D9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="E9" t="n">
-        <v>315010</v>
-      </c>
-      <c r="F9" t="n">
-        <v>7.42</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4.15</v>
+        <v>62</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>aspoň 85 %</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>neúplný rok – do data snímku; způsoby jen jako pásmo podílu (pod prahem)</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2021 – podniky FO</t>
+          <t>Česko – 2023</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>154046</v>
+        <v>1319</v>
       </c>
       <c r="C10" t="n">
-        <v>7.82</v>
+        <v>366</v>
       </c>
       <c r="D10" t="n">
-        <v>6.46</v>
+        <v>953</v>
       </c>
       <c r="E10" t="n">
-        <v>918884</v>
+        <v>909</v>
       </c>
       <c r="F10" t="n">
-        <v>9.07</v>
+        <v>44</v>
       </c>
       <c r="G10" t="n">
-        <v>6.3</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2021 – podniky PO</t>
+          <t>Česko – 2024</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>35822</v>
+        <v>1373</v>
       </c>
       <c r="C11" t="n">
-        <v>7.52</v>
+        <v>513</v>
       </c>
       <c r="D11" t="n">
-        <v>3.42</v>
+        <v>860</v>
       </c>
       <c r="E11" t="n">
-        <v>334396</v>
+        <v>820</v>
       </c>
       <c r="F11" t="n">
-        <v>7.98</v>
+        <v>40</v>
       </c>
       <c r="G11" t="n">
-        <v>3.85</v>
+        <v>37.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2022 – podniky FO</t>
+          <t>Česko – 2025</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>158250</v>
+        <v>1429</v>
       </c>
       <c r="C12" t="n">
-        <v>8.85</v>
+        <v>625</v>
       </c>
       <c r="D12" t="n">
-        <v>7.75</v>
+        <v>804</v>
       </c>
       <c r="E12" t="n">
-        <v>946485</v>
+        <v>749</v>
       </c>
       <c r="F12" t="n">
-        <v>9.69</v>
+        <v>55</v>
       </c>
       <c r="G12" t="n">
-        <v>7.71</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2022 – podniky PO</t>
+          <t>Česko – 2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>37480</v>
+        <v>1142</v>
       </c>
       <c r="C13" t="n">
-        <v>7.22</v>
+        <v>514</v>
       </c>
       <c r="D13" t="n">
-        <v>3.43</v>
+        <v>628</v>
       </c>
       <c r="E13" t="n">
-        <v>344989</v>
+        <v>573</v>
       </c>
       <c r="F13" t="n">
-        <v>7.21</v>
+        <v>55</v>
       </c>
       <c r="G13" t="n">
-        <v>3.96</v>
+        <v>45</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>neúplný rok – do data snímku</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Způsob zániku podle RES (číselník 572, ZPZAN). Kód 04 = zrušení právnické osoby bez likvidace bez nástupců; zahrnuje i výmaz společnosti rejstříkovým soudem bez likvidace. Jiný způsob = přeměna (02, 03) a ostatní kódy včetně nezjištěného.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Pomlčka = skryto: počet pod prahem nebo by z něj šel dopočítat jiný skrytý počet. Pásmo podílu („aspoň“, „nejvýš“) se uvádí místo přesného podílu, když je jedna z částí pod prahem.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Míra zániku právnických osob – obor a všechny ostatní obory, celkem a bez kódu 04 (RES)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zdroj: Český statistický úřad, Registr ekonomických subjektů (RES) – otevřená data, stav k 15. 10. 2026; licence CC BY 4.0 (https://csu.gov.cz/podminky_pro_vyuzivani_a_dalsi_zverejnovani_statistickych_udaju_csu); vlastní výpočet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Odvozené údaje, nejde o oficiální statistiku ČSÚ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Položka</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Stav PO k 1. 1.</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Míra zániku za rok (%)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Za rok bez kódu 04 (%)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Míra zániku 1. 1.–15. 10. (%)</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1. 1.–15. 10. bez kódu 04 (%)</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Poznámka</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Obor – Liberecký kraj – 2023</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1663</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>pod 0,7 %</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>část skryta (práh, dopočet); bez kódu 04 pod prahem – jen pásmo</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Obor – Liberecký kraj – 2024</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1720</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>pod 0,6 %</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>pod 0,6 %</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>bez kódu 04 pod prahem – jen pásmo</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Obor – Liberecký kraj – 2025</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1739</v>
+      </c>
+      <c r="C8" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>pod 0,6 %</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>pod 0,6 %</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>bez kódu 04 pod prahem – jen pásmo</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Obor – Liberecký kraj – 2026</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1704</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>pod 0,6 %</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>neúplný rok – jen srovnatelné období; bez kódu 04 pod prahem – jen pásmo</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Ostatní obory – Liberecký kraj – 2023</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>22946</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Ostatní obory – Liberecký kraj – 2024</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>23148</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ostatní obory – Liberecký kraj – 2025</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>23305</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Ostatní obory – Liberecký kraj – 2026</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>22870</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>neúplný rok – jen srovnatelné období</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2023 – podniky FO</t>
+          <t>Obor – Česko – 2023</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>162083</v>
+        <v>50946</v>
       </c>
       <c r="C14" t="n">
-        <v>9.59</v>
+        <v>2.59</v>
       </c>
       <c r="D14" t="n">
-        <v>9.050000000000001</v>
+        <v>1.87</v>
       </c>
       <c r="E14" t="n">
-        <v>968178</v>
+        <v>2.02</v>
       </c>
       <c r="F14" t="n">
-        <v>9.83</v>
-      </c>
-      <c r="G14" t="n">
-        <v>8.789999999999999</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>předběžné hodnoty</t>
-        </is>
+        <v>1.48</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2023 – podniky PO</t>
+          <t>Obor – Česko – 2024</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>39445</v>
+        <v>52622</v>
       </c>
       <c r="C15" t="n">
-        <v>7.36</v>
+        <v>2.61</v>
       </c>
       <c r="D15" t="n">
-        <v>4.55</v>
+        <v>1.63</v>
       </c>
       <c r="E15" t="n">
-        <v>353778</v>
+        <v>1.99</v>
       </c>
       <c r="F15" t="n">
-        <v>7.02</v>
-      </c>
-      <c r="G15" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>předběžné hodnoty</t>
-        </is>
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Obor – Česko – 2025</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>54450</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Jiná jednotka: aktivní PODNIK ze statistiky demografie podniků, ne registrovaný ekonomický subjekt z RES; čísla nejsou srovnatelná s ostatními tabulkami. Jen za ČR.</t>
+          <t>Obor – Česko – 2026</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>56779</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>neúplný rok – jen srovnatelné období</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ostatní obory – Česko – 2023</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>757945</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Ostatní obory – Česko – 2024</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>768507</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ostatní obory – Česko – 2025</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>779504</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Ostatní obory – Česko – 2026</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>790826</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>neúplný rok – jen srovnatelné období</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ostatní obory = všechny právnické osoby území s určeným oborem (CZ-NACE 2025) mimo zkoumaný obor; míra se počítá stejnou metodou jako míra zániku oboru (T18): zaniklé PO v roce / stav PO k 1. 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Bez kódu 04 = zániky jiným způsobem než zrušením bez likvidace bez nástupců (ZPZAN 04), vztažené ke stejnému stavu PO k 1. 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Pásmo „pod X %“ = počet zániků bez kódu 04 je pod prahem; X je práh dělený stavem PO.</t>
         </is>
       </c>
     </row>
@@ -6758,23 +6975,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Zjištění detektoru (seřazeno podle síly)</t>
+          <t>Vznik a zánik ekonomických subjektů v území – všechny obory (ČSÚ, RES05)</t>
         </is>
       </c>
     </row>
@@ -6800,35 +7014,20 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Zjištění</t>
+          <t>FO</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Typ zjištění</t>
+          <t>PO</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Síla</t>
+          <t>Celkem</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Hodnota</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Srovnání</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Relativní rozdíl (%)</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Poznámka</t>
         </is>
@@ -6837,961 +7036,150 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Míra zániku PO v oboru se mezi lety 2023 a 2025 změnila v Libereckém kraji z 2,1 % na 5,92 % (index 2,82), v Česku z 2,59 % na 2,62 % (index 1,01); index je relativně o 179,2 % vyšší než v Česku.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ZTR-IMTV</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>změna trendu</t>
-        </is>
+          <t>2023 – vzniklé</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2859</v>
+      </c>
+      <c r="C6" t="n">
+        <v>785</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7921</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="G6" t="n">
-        <v>179.2</v>
+        <v>3644</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Míra zániku PO v oboru za rok 2025 je v Libereckém kraji 5,92 %, průměr let 2023–2024 je 2,48 % (relativně o 138,7 % vyšší).</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>ZTR-CISP</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>změna trendu</t>
-        </is>
+          <t>2023 – zaniklé</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>13252</v>
+      </c>
+      <c r="C7" t="n">
+        <v>483</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3871</v>
-      </c>
-      <c r="E7" t="n">
-        <v>5.92</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="G7" t="n">
-        <v>138.7</v>
+        <v>13735</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>mimořádný výkyv: hromadný zánik FO v 1. čtvrtletí 2023</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Míra zániku PO v oboru za rok 2025 je v Libereckém kraji 5,92 %, v Česku 2,62 % (relativně o 126 % vyšší).</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ZTR-LQXC</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>změna trendu</t>
-        </is>
+          <t>2024 – vzniklé</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3326</v>
+      </c>
+      <c r="C8" t="n">
+        <v>768</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2595</v>
-      </c>
-      <c r="E8" t="n">
-        <v>5.92</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="G8" t="n">
-        <v>126</v>
+        <v>4094</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kraj je mezi 14 kraji 13. podle počtu registrovaných subjektů oboru a 2. podle hustoty na 1 000 obyvatel.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>ZPO-QDHA</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>divergence pořadí</t>
-        </is>
+          <t>2024 – zaniklé</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3390</v>
+      </c>
+      <c r="C9" t="n">
+        <v>582</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8462</v>
-      </c>
-      <c r="E9" t="n">
-        <v>13</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2</v>
+        <v>3972</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Míra zániku PO v oboru za období 1. 1.–15. 10. 2026 je v Libereckém kraji 3,64 %, v Česku 2,01 % (relativně o 81,1 % vyšší).</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>ZTR-HJID</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>změna trendu</t>
-        </is>
+          <t>2025 – vzniklé</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3239</v>
+      </c>
+      <c r="C10" t="n">
+        <v>766</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8109</v>
-      </c>
-      <c r="E10" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="F10" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="G10" t="n">
-        <v>81.09999999999999</v>
+        <v>4005</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nejvyšší hustotu oboru mezi okresy kraje má okres Jablonec nad Nisou (36,09 na 1 000 obyvatel), nejnižší okres Česká Lípa (25,76); hustota v okrese Jablonec nad Nisou je relativně o 40,1 % vyšší než v okrese Česká Lípa.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>ZUZ-EGWN</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>rozdíly uvnitř území</t>
-        </is>
+          <t>2025 – zaniklé</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2003</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1221</v>
       </c>
       <c r="D11" t="n">
-        <v>0.401</v>
-      </c>
-      <c r="E11" t="n">
-        <v>36.09</v>
-      </c>
-      <c r="F11" t="n">
-        <v>25.76</v>
-      </c>
-      <c r="G11" t="n">
-        <v>40.1</v>
+        <v>3224</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Typ osoby – „právnické osoby a ostatní (PO)“: podíl na registrovaných subjektech oboru je v Libereckém kraji 11,6 %, v Česku 17,3 % (relativně o 32,9 % nižší).</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>ZOD-SXHQ</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>odchylka od ČR</t>
-        </is>
+          <t>2026 – vzniklé</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1880</v>
+      </c>
+      <c r="C12" t="n">
+        <v>425</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3295</v>
-      </c>
-      <c r="E12" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="F12" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="G12" t="n">
-        <v>32.9</v>
+        <v>2305</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2 čtvrtletí</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Právní forma – „112 Společnost s ručením omezeným“: podíl na registrovaných subjektech oboru je v Libereckém kraji 11 %, v Česku 16,4 % (relativně o 32,9 % nižší).</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>ZOD-SRRX</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>odchylka od ČR</t>
-        </is>
+          <t>2026 – zaniklé</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>850</v>
+      </c>
+      <c r="C13" t="n">
+        <v>516</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3293</v>
-      </c>
-      <c r="E13" t="n">
-        <v>11</v>
-      </c>
-      <c r="F13" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="G13" t="n">
-        <v>32.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Věk subjektu – „31 a více let“: podíl na registrovaných subjektech oboru je v Libereckém kraji 19,5 %, v Česku 15,6 % (relativně o 25 % vyšší).</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>ZOD-CAID</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>odchylka od ČR</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E14" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="F14" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="G14" t="n">
-        <v>25</v>
+        <v>1366</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2 čtvrtletí</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Na 1 000 obyvatel připadá v okrese Česká Lípa 25,76 registrovaných subjektů oboru, v Libereckém kraji 32,99 (relativně o 21,9 % nižší).</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>ZUZ-OWLP</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>rozdíly uvnitř území</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>0.2192</v>
-      </c>
-      <c r="E15" t="n">
-        <v>25.76</v>
-      </c>
-      <c r="F15" t="n">
-        <v>32.99</v>
-      </c>
-      <c r="G15" t="n">
-        <v>21.9</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Lokalizační koeficient oboru je v Libereckém kraji 1,2 proti 1 za ČR (relativně o 20 % vyšší).</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>ZOD-PUOD</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>odchylka od ČR</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Věk subjektu – „méně než 3 roky“: podíl na registrovaných subjektech oboru je v Libereckém kraji 11,4 %, v Česku 14 % (relativně o 18,6 % nižší).</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>ZOD-YZQO</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>odchylka od ČR</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>0.1857</v>
-      </c>
-      <c r="E17" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="F17" t="n">
-        <v>14</v>
-      </c>
-      <c r="G17" t="n">
-        <v>18.6</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Na 1 000 obyvatel připadá v okrese Česká Lípa 25,76 registrovaných subjektů oboru, v Česku 31,15 (relativně o 17,3 % nižší).</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>ZUZ-ADGK</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>rozdíly uvnitř území</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>0.173</v>
-      </c>
-      <c r="E18" t="n">
-        <v>25.76</v>
-      </c>
-      <c r="F18" t="n">
-        <v>31.15</v>
-      </c>
-      <c r="G18" t="n">
-        <v>17.3</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Sekce F tvořila v roce 2022 v Libereckém kraji 4,44 % zaměstnanců (přepočtené počty), v Česku 5,33 % (relativně o 16,7 % nižší).</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>ZMZ-ULLF</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>mzdy a zaměstnanost</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="E19" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="F19" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="G19" t="n">
-        <v>16.7</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Na 1 000 obyvatel připadá v okrese Jablonec nad Nisou 36,09 registrovaných subjektů oboru, v Česku 31,15 (relativně o 15,9 % vyšší).</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>ZUZ-DHYT</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>rozdíly uvnitř území</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>0.1586</v>
-      </c>
-      <c r="E20" t="n">
-        <v>36.09</v>
-      </c>
-      <c r="F20" t="n">
-        <v>31.15</v>
-      </c>
-      <c r="G20" t="n">
-        <v>15.9</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Na 1 000 obyvatel připadá v okrese Liberec 36,04 registrovaných subjektů oboru, v Česku 31,15 (relativně o 15,7 % vyšší).</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>ZUZ-OXBR</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>rozdíly uvnitř území</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>0.157</v>
-      </c>
-      <c r="E21" t="n">
-        <v>36.04</v>
-      </c>
-      <c r="F21" t="n">
-        <v>31.15</v>
-      </c>
-      <c r="G21" t="n">
-        <v>15.7</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Velikost PO – „1–9 zaměstnanců“: podíl na PO oboru je v Libereckém kraji 44,6 %, v Česku 39,1 % (relativně o 14,1 % vyšší).</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>ZOD-TOQY</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>odchylka od ČR</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>0.1407</v>
-      </c>
-      <c r="E22" t="n">
-        <v>44.6</v>
-      </c>
-      <c r="F22" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="G22" t="n">
-        <v>14.1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Velikost PO – „Neuvedeno“: podíl na PO oboru je v Libereckém kraji 44,6 %, v Česku 50,1 % (relativně o 11 % nižší).</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>ZOD-NDPG</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>odchylka od ČR</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>0.1098</v>
-      </c>
-      <c r="E23" t="n">
-        <v>44.6</v>
-      </c>
-      <c r="F23" t="n">
-        <v>50.1</v>
-      </c>
-      <c r="G23" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Na 1 000 obyvatel připadá v okrese Jablonec nad Nisou 36,09 registrovaných subjektů oboru, v Libereckém kraji 32,99 (relativně o 9,4 % vyšší).</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>ZUZ-CLRE</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>rozdíly uvnitř území</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="E24" t="n">
-        <v>36.09</v>
-      </c>
-      <c r="F24" t="n">
-        <v>32.99</v>
-      </c>
-      <c r="G24" t="n">
-        <v>9.4</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Na 1 000 obyvatel připadá v okrese Liberec 36,04 registrovaných subjektů oboru, v Libereckém kraji 32,99 (relativně o 9,2 % vyšší).</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>ZUZ-HFUA</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>rozdíly uvnitř území</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>0.0925</v>
-      </c>
-      <c r="E25" t="n">
-        <v>36.04</v>
-      </c>
-      <c r="F25" t="n">
-        <v>32.99</v>
-      </c>
-      <c r="G25" t="n">
-        <v>9.199999999999999</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Právní forma – „101 Fyzická osoba podnikající dle živnostenského zákona“: podíl na registrovaných subjektech oboru je v Libereckém kraji 86,1 %, v Česku 79,2 % (relativně o 8,7 % vyšší).</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>ZOD-DWBZ</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>odchylka od ČR</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>0.0871</v>
-      </c>
-      <c r="E26" t="n">
-        <v>86.09999999999999</v>
-      </c>
-      <c r="F26" t="n">
-        <v>79.2</v>
-      </c>
-      <c r="G26" t="n">
-        <v>8.699999999999999</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Věk subjektu – „11–20 let“: podíl na registrovaných subjektech oboru je v Libereckém kraji 22,1 %, v Česku 23,9 % (relativně o 7,5 % nižší).</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>ZOD-SMOT</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>odchylka od ČR</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>0.07530000000000001</v>
-      </c>
-      <c r="E27" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="F27" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="G27" t="n">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Typ osoby – „fyzické osoby (FO)“: podíl na registrovaných subjektech oboru je v Libereckém kraji 88,4 %, v Česku 82,7 % (relativně o 6,9 % vyšší).</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>ZOD-KHDN</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>odchylka od ČR</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>0.0689</v>
-      </c>
-      <c r="E28" t="n">
-        <v>88.40000000000001</v>
-      </c>
-      <c r="F28" t="n">
-        <v>82.7</v>
-      </c>
-      <c r="G28" t="n">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Průměrná mzda v sekci F dosahovala v roce 2022 v Libereckém kraji 91,5 % průměrné mzdy všech odvětví kraje, v Česku 85,8 % (relativně o 6,6 % vyšší).</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>ZMZ-TZVU</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>mzdy a zaměstnanost</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>0.0664</v>
-      </c>
-      <c r="E29" t="n">
-        <v>91.5</v>
-      </c>
-      <c r="F29" t="n">
-        <v>85.8</v>
-      </c>
-      <c r="G29" t="n">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Podíl registrovaných subjektů se zjištěnou aktivitou je v Libereckém kraji v sekci F 62,3 %, ve všech oborech 58,8 % (ČSÚ; relativně o 6 % vyšší).</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>ZAK-UMSL</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>aktivita oboru vůči kraji</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>0.0595</v>
-      </c>
-      <c r="E30" t="n">
-        <v>62.3</v>
-      </c>
-      <c r="F30" t="n">
-        <v>58.8</v>
-      </c>
-      <c r="G30" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Na 1 000 obyvatel připadá v Libereckém kraji 32,99 registrovaných subjektů oboru, v Česku 31,15 (relativně o 5,9 % vyšší).</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>ZOD-YNST</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>odchylka od ČR</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>0.0591</v>
-      </c>
-      <c r="E31" t="n">
-        <v>32.99</v>
-      </c>
-      <c r="F31" t="n">
-        <v>31.15</v>
-      </c>
-      <c r="G31" t="n">
-        <v>5.9</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Velikost PO – „10–49 zaměstnanců“: podíl na PO oboru je v Libereckém kraji 10 %, v Česku 9,5 % (relativně o 5,3 % vyšší).</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>ZOD-JLNI</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>odchylka od ČR</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>0.0526</v>
-      </c>
-      <c r="E32" t="n">
-        <v>10</v>
-      </c>
-      <c r="F32" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G32" t="n">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Věk subjektu – „3–5 let“: podíl na registrovaných subjektech oboru je v Libereckém kraji 9,4 %, v Česku 9,9 % (relativně o 5,1 % nižší).</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>ZOD-DKSF</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>odchylka od ČR</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>0.0505</v>
-      </c>
-      <c r="E33" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="F33" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="G33" t="n">
-        <v>5.1</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Na 1 000 obyvatel připadá v okrese Semily 31,58 registrovaných subjektů oboru, v Libereckém kraji 32,99 (relativně o 4,3 % nižší).</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>ZUZ-LRXD</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>rozdíly uvnitř území</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>0.0427</v>
-      </c>
-      <c r="E34" t="n">
-        <v>31.58</v>
-      </c>
-      <c r="F34" t="n">
-        <v>32.99</v>
-      </c>
-      <c r="G34" t="n">
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>V sekci F se počet zaměstnanců mezi lety 2018 a 2022 změnil v Libereckém kraji z 6 tis. na 6,4 tis. (index 1,07), v Česku z 207,9 tis. na 214,9 tis. (index 1,03); index je relativně o 3,9 % vyšší než v Česku.</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>ZMZ-MXTD</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>mzdy a zaměstnanost</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>0.0388</v>
-      </c>
-      <c r="E35" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="F35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="G35" t="n">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Objem hrubé přidané hodnoty skupiny Stavebnictví (F) se mezi lety 2020 a 2024 změnil v Libereckém kraji na 89,8 % (rok 2020 = 100), v Česku na 93,1 % (relativně o 3,5 % nižší).</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>ZEK-YCEY</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>ekonomika</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>0.0354</v>
-      </c>
-      <c r="E36" t="n">
-        <v>89.8</v>
-      </c>
-      <c r="F36" t="n">
-        <v>93.09999999999999</v>
-      </c>
-      <c r="G36" t="n">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Průměrná hrubá měsíční mzda v sekci F byla v roce 2022 v Libereckém kraji 33 623 Kč, v Česku 34 840 Kč (relativně o 3,5 % nižší).</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>ZMZ-KWKY</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>mzdy a zaměstnanost</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>0.0349</v>
-      </c>
-      <c r="E37" t="n">
-        <v>33623</v>
-      </c>
-      <c r="F37" t="n">
-        <v>34840</v>
-      </c>
-      <c r="G37" t="n">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Velikost FO – „Neuvedeno“: podíl na FO oboru je v Libereckém kraji 45,8 %, v Česku 44,3 % (relativně o 3,4 % vyšší).</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>ZOD-DHJV</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>odchylka od ČR</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>0.0339</v>
-      </c>
-      <c r="E38" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="F38" t="n">
-        <v>44.3</v>
-      </c>
-      <c r="G38" t="n">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Síla = |hodnota / srovnání − 1|; u divergence pořadí |p1 − p2| / (počet území − 1). Rozdíly pod 3 % relativně se nehlásí. Položky struktury s podílem pod 5 % v území i v ČR se nehlásí. Popisy jsou věcné, bez interpretace.</t>
+          <t>ČSÚ nepublikuje vznik a zánik v členění podle oboru (kraj × sekce); jde o celé území. Čísla FO a PO pod prahem se nezveřejňují (zůstává jen celkem).</t>
         </is>
       </c>
     </row>
@@ -8036,7 +7424,1514 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K78"/>
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Demografie podniků v ČR – kontext (ČSÚ, RESDP00; jednotka podnik)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zdroj: Český statistický úřad, Registr ekonomických subjektů (RES) – otevřená data, stav k 15. 10. 2026; licence CC BY 4.0 (https://csu.gov.cz/podminky_pro_vyuzivani_a_dalsi_zverejnovani_statistickych_udaju_csu); vlastní výpočet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Odvozené údaje, nejde o oficiální statistiku ČSÚ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Položka</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Stavebnictví: aktivní podniky</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Stavebnictví: míra vzniků (%)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Stavebnictví: míra zániků (%)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Všechna odvětví: aktivní podniky</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Všechna odvětví: míra vzniků (%)</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Všechna odvětví: míra zániků (%)</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Poznámka</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2019 – podniky FO</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>151021</v>
+      </c>
+      <c r="C6" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="E6" t="n">
+        <v>903037</v>
+      </c>
+      <c r="F6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G6" t="n">
+        <v>7.84</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2019 – podniky PO</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>32611</v>
+      </c>
+      <c r="C7" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="E7" t="n">
+        <v>306300</v>
+      </c>
+      <c r="F7" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3.73</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2020 – podniky FO</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>151683</v>
+      </c>
+      <c r="C8" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="E8" t="n">
+        <v>906249</v>
+      </c>
+      <c r="F8" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="G8" t="n">
+        <v>7.69</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2020 – podniky PO</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>34021</v>
+      </c>
+      <c r="C9" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="E9" t="n">
+        <v>315010</v>
+      </c>
+      <c r="F9" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4.15</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2021 – podniky FO</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>154046</v>
+      </c>
+      <c r="C10" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="E10" t="n">
+        <v>918884</v>
+      </c>
+      <c r="F10" t="n">
+        <v>9.07</v>
+      </c>
+      <c r="G10" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2021 – podniky PO</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>35822</v>
+      </c>
+      <c r="C11" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="E11" t="n">
+        <v>334396</v>
+      </c>
+      <c r="F11" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2022 – podniky FO</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>158250</v>
+      </c>
+      <c r="C12" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="D12" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="E12" t="n">
+        <v>946485</v>
+      </c>
+      <c r="F12" t="n">
+        <v>9.69</v>
+      </c>
+      <c r="G12" t="n">
+        <v>7.71</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2022 – podniky PO</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>37480</v>
+      </c>
+      <c r="C13" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="E13" t="n">
+        <v>344989</v>
+      </c>
+      <c r="F13" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3.96</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2023 – podniky FO</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>162083</v>
+      </c>
+      <c r="C14" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="D14" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="E14" t="n">
+        <v>968178</v>
+      </c>
+      <c r="F14" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="G14" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>předběžné hodnoty</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2023 – podniky PO</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>39445</v>
+      </c>
+      <c r="C15" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="E15" t="n">
+        <v>353778</v>
+      </c>
+      <c r="F15" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>předběžné hodnoty</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Jiná jednotka: aktivní PODNIK ze statistiky demografie podniků, ne registrovaný ekonomický subjekt z RES; čísla nejsou srovnatelná s ostatními tabulkami. Jen za ČR.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="50" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Zjištění detektoru (seřazeno podle síly)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zdroj: Český statistický úřad, Registr ekonomických subjektů (RES) – otevřená data, stav k 15. 10. 2026; licence CC BY 4.0 (https://csu.gov.cz/podminky_pro_vyuzivani_a_dalsi_zverejnovani_statistickych_udaju_csu); vlastní výpočet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Odvozené údaje, nejde o oficiální statistiku ČSÚ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Položka</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Zjištění</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Typ zjištění</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Síla</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Hodnota</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Srovnání</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Relativní rozdíl (%)</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Jev oboru nebo území</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Síla před snížením</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Ostatní obory: hodnota</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Ostatní obory: srovnání</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Ostatní obory: relativní rozdíl (%)</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Poznámka</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Kraj je mezi 14 kraji 13. podle počtu registrovaných subjektů oboru a 2. podle hustoty na 1 000 obyvatel.</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ZPO-QDHA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>divergence pořadí</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.8462</v>
+      </c>
+      <c r="E6" t="n">
+        <v>13</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Nejvyšší hustotu oboru mezi okresy kraje má okres Jablonec nad Nisou (36,09 na 1 000 obyvatel), nejnižší okres Česká Lípa (25,76); hustota v okrese Jablonec nad Nisou je relativně o 40,1 % vyšší než v okrese Česká Lípa.</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ZUZ-EGWN</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>rozdíly uvnitř území</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="E7" t="n">
+        <v>36.09</v>
+      </c>
+      <c r="F7" t="n">
+        <v>25.76</v>
+      </c>
+      <c r="G7" t="n">
+        <v>40.1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Typ osoby – „právnické osoby a ostatní (PO)“: podíl na registrovaných subjektech oboru je v Libereckém kraji 11,6 %, v Česku 17,3 % (relativně o 32,9 % nižší).</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ZOD-SXHQ</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>odchylka od ČR</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="E8" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="F8" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="G8" t="n">
+        <v>32.9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Právní forma – „112 Společnost s ručením omezeným“: podíl na registrovaných subjektech oboru je v Libereckém kraji 11 %, v Česku 16,4 % (relativně o 32,9 % nižší).</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ZOD-SRRX</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>odchylka od ČR</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="E9" t="n">
+        <v>11</v>
+      </c>
+      <c r="F9" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="G9" t="n">
+        <v>32.9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Míra zániku PO v oboru za rok 2025 je v Libereckém kraji 5,92 %, v Česku 2,62 % (relativně o 126 % vyšší). Ve všech ostatních oborech je míra zániku PO za rok 2025 v Libereckém kraji 4,8 %, v Česku 2,66 % (relativně o 80,5 % vyšší) – jev celého kraje, ne oboru.</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ZTR-LQXC</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>změna trendu</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.2522</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="G10" t="n">
+        <v>126</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>území</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.2595</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="L10" t="n">
+        <v>80.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Věk subjektu – „31 a více let“: podíl na registrovaných subjektech oboru je v Libereckém kraji 19,5 %, v Česku 15,6 % (relativně o 25 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ZOD-CAID</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>odchylka od ČR</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="G11" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Míra zániku PO v oboru za období 1. 1.–15. 10. 2026 je v Libereckém kraji 3,64 %, v Česku 2,01 % (relativně o 81,1 % vyšší). Ve všech ostatních oborech je míra zániku PO za období 1. 1.–15. 10. 2026 v Libereckém kraji 2,86 %, v Česku 1,97 % (relativně o 45,2 % vyšší) – jev celého kraje, ne oboru.</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ZTR-HJID</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>změna trendu</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.2474</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="G12" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>území</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0.8109</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="L12" t="n">
+        <v>45.2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Na 1 000 obyvatel připadá v okrese Česká Lípa 25,76 registrovaných subjektů oboru, v Libereckém kraji 32,99 (relativně o 21,9 % nižší).</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ZUZ-OWLP</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>rozdíly uvnitř území</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.2192</v>
+      </c>
+      <c r="E13" t="n">
+        <v>25.76</v>
+      </c>
+      <c r="F13" t="n">
+        <v>32.99</v>
+      </c>
+      <c r="G13" t="n">
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Lokalizační koeficient oboru je v Libereckém kraji 1,2 proti 1 za ČR (relativně o 20 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ZOD-PUOD</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>odchylka od ČR</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Míra zániku PO v oboru se mezi lety 2023 a 2025 změnila v Libereckém kraji z 2,1 % na 5,92 % (index 2,82), v Česku z 2,59 % na 2,62 % (index 1,01); index je relativně o 179,2 % vyšší než v Česku. Ve všech ostatních oborech se míra zániku PO mezi lety 2023 a 2025 změnila v Libereckém kraji s indexem 2,47, v Česku s indexem 1,06; index je relativně o 133 % vyšší než v Česku – jev celého kraje, ne oboru.</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ZTR-IMTV</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>změna trendu</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.1982</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G15" t="n">
+        <v>179.2</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>území</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.7921</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L15" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Věk subjektu – „méně než 3 roky“: podíl na registrovaných subjektech oboru je v Libereckém kraji 11,4 %, v Česku 14 % (relativně o 18,6 % nižší).</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ZOD-YZQO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>odchylka od ČR</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.1857</v>
+      </c>
+      <c r="E16" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="F16" t="n">
+        <v>14</v>
+      </c>
+      <c r="G16" t="n">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Na 1 000 obyvatel připadá v okrese Česká Lípa 25,76 registrovaných subjektů oboru, v Česku 31,15 (relativně o 17,3 % nižší).</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ZUZ-ADGK</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>rozdíly uvnitř území</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.173</v>
+      </c>
+      <c r="E17" t="n">
+        <v>25.76</v>
+      </c>
+      <c r="F17" t="n">
+        <v>31.15</v>
+      </c>
+      <c r="G17" t="n">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Sekce F tvořila v roce 2022 v Libereckém kraji 4,44 % zaměstnanců (přepočtené počty), v Česku 5,33 % (relativně o 16,7 % nižší).</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ZMZ-ULLF</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>mzdy a zaměstnanost</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="E18" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="F18" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="G18" t="n">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Na 1 000 obyvatel připadá v okrese Jablonec nad Nisou 36,09 registrovaných subjektů oboru, v Česku 31,15 (relativně o 15,9 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ZUZ-DHYT</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>rozdíly uvnitř území</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="E19" t="n">
+        <v>36.09</v>
+      </c>
+      <c r="F19" t="n">
+        <v>31.15</v>
+      </c>
+      <c r="G19" t="n">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Na 1 000 obyvatel připadá v okrese Liberec 36,04 registrovaných subjektů oboru, v Česku 31,15 (relativně o 15,7 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ZUZ-OXBR</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>rozdíly uvnitř území</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="E20" t="n">
+        <v>36.04</v>
+      </c>
+      <c r="F20" t="n">
+        <v>31.15</v>
+      </c>
+      <c r="G20" t="n">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Velikost PO – „1–9 zaměstnanců“: podíl na PO oboru je v Libereckém kraji 44,6 %, v Česku 39,1 % (relativně o 14,1 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ZOD-TOQY</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>odchylka od ČR</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.1407</v>
+      </c>
+      <c r="E21" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="F21" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Velikost PO – „Neuvedeno“: podíl na PO oboru je v Libereckém kraji 44,6 %, v Česku 50,1 % (relativně o 11 % nižší).</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ZOD-NDPG</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>odchylka od ČR</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0.1098</v>
+      </c>
+      <c r="E22" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="F22" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Na 1 000 obyvatel připadá v okrese Jablonec nad Nisou 36,09 registrovaných subjektů oboru, v Libereckém kraji 32,99 (relativně o 9,4 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ZUZ-CLRE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>rozdíly uvnitř území</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="E23" t="n">
+        <v>36.09</v>
+      </c>
+      <c r="F23" t="n">
+        <v>32.99</v>
+      </c>
+      <c r="G23" t="n">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Na 1 000 obyvatel připadá v okrese Liberec 36,04 registrovaných subjektů oboru, v Libereckém kraji 32,99 (relativně o 9,2 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ZUZ-HFUA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>rozdíly uvnitř území</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.0925</v>
+      </c>
+      <c r="E24" t="n">
+        <v>36.04</v>
+      </c>
+      <c r="F24" t="n">
+        <v>32.99</v>
+      </c>
+      <c r="G24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Právní forma – „101 Fyzická osoba podnikající dle živnostenského zákona“: podíl na registrovaných subjektech oboru je v Libereckém kraji 86,1 %, v Česku 79,2 % (relativně o 8,7 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ZOD-DWBZ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>odchylka od ČR</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.0871</v>
+      </c>
+      <c r="E25" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="F25" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="G25" t="n">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Věk subjektu – „11–20 let“: podíl na registrovaných subjektech oboru je v Libereckém kraji 22,1 %, v Česku 23,9 % (relativně o 7,5 % nižší).</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ZOD-SMOT</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>odchylka od ČR</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0.07530000000000001</v>
+      </c>
+      <c r="E26" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="G26" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Typ osoby – „fyzické osoby (FO)“: podíl na registrovaných subjektech oboru je v Libereckém kraji 88,4 %, v Česku 82,7 % (relativně o 6,9 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ZOD-KHDN</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>odchylka od ČR</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0.0689</v>
+      </c>
+      <c r="E27" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="F27" t="n">
+        <v>82.7</v>
+      </c>
+      <c r="G27" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Průměrná mzda v sekci F dosahovala v roce 2022 v Libereckém kraji 91,5 % průměrné mzdy všech odvětví kraje, v Česku 85,8 % (relativně o 6,6 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ZMZ-TZVU</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>mzdy a zaměstnanost</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0.0664</v>
+      </c>
+      <c r="E28" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="G28" t="n">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Podíl registrovaných subjektů se zjištěnou aktivitou je v Libereckém kraji v sekci F 62,3 %, ve všech oborech 58,8 % (ČSÚ; relativně o 6 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ZAK-UMSL</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>aktivita oboru vůči kraji</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0.0595</v>
+      </c>
+      <c r="E29" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="F29" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="G29" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Na 1 000 obyvatel připadá v Libereckém kraji 32,99 registrovaných subjektů oboru, v Česku 31,15 (relativně o 5,9 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ZOD-YNST</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>odchylka od ČR</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.0591</v>
+      </c>
+      <c r="E30" t="n">
+        <v>32.99</v>
+      </c>
+      <c r="F30" t="n">
+        <v>31.15</v>
+      </c>
+      <c r="G30" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Velikost PO – „10–49 zaměstnanců“: podíl na PO oboru je v Libereckém kraji 10 %, v Česku 9,5 % (relativně o 5,3 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ZOD-JLNI</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>odchylka od ČR</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.0526</v>
+      </c>
+      <c r="E31" t="n">
+        <v>10</v>
+      </c>
+      <c r="F31" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G31" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Věk subjektu – „3–5 let“: podíl na registrovaných subjektech oboru je v Libereckém kraji 9,4 %, v Česku 9,9 % (relativně o 5,1 % nižší).</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ZOD-DKSF</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>odchylka od ČR</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0.0505</v>
+      </c>
+      <c r="E32" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="F32" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="G32" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Míra zániku PO v oboru za rok 2025 je v Libereckém kraji 5,92 %, průměr let 2023–2024 je 2,48 % (relativně o 138,7 % vyšší). Ve všech ostatních oborech je v Libereckém kraji míra zániku PO za rok 2025 4,8 %, průměr let 2023–2024 2,11 % (relativně o 127,5 % vyšší) – jev celého kraje, ne oboru.</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ZTR-CISP</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>změna trendu</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0.0493</v>
+      </c>
+      <c r="E33" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G33" t="n">
+        <v>138.7</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>území</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>1.3871</v>
+      </c>
+      <c r="J33" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="L33" t="n">
+        <v>127.5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Na 1 000 obyvatel připadá v okrese Semily 31,58 registrovaných subjektů oboru, v Libereckém kraji 32,99 (relativně o 4,3 % nižší).</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ZUZ-LRXD</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>rozdíly uvnitř území</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0.0427</v>
+      </c>
+      <c r="E34" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="F34" t="n">
+        <v>32.99</v>
+      </c>
+      <c r="G34" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>V sekci F se počet zaměstnanců mezi lety 2018 a 2022 změnil v Libereckém kraji z 6 tis. na 6,4 tis. (index 1,07), v Česku z 207,9 tis. na 214,9 tis. (index 1,03); index je relativně o 3,9 % vyšší než v Česku.</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ZMZ-MXTD</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>mzdy a zaměstnanost</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0.0388</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Objem hrubé přidané hodnoty skupiny Stavebnictví (F) se mezi lety 2020 a 2024 změnil v Libereckém kraji na 89,8 % (rok 2020 = 100), v Česku na 93,1 % (relativně o 3,5 % nižší).</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ZEK-YCEY</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ekonomika</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0.0354</v>
+      </c>
+      <c r="E36" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="F36" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="G36" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Průměrná hrubá měsíční mzda v sekci F byla v roce 2022 v Libereckém kraji 33 623 Kč, v Česku 34 840 Kč (relativně o 3,5 % nižší).</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ZMZ-KWKY</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>mzdy a zaměstnanost</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0.0349</v>
+      </c>
+      <c r="E37" t="n">
+        <v>33623</v>
+      </c>
+      <c r="F37" t="n">
+        <v>34840</v>
+      </c>
+      <c r="G37" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Velikost FO – „Neuvedeno“: podíl na FO oboru je v Libereckém kraji 45,8 %, v Česku 44,3 % (relativně o 3,4 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ZOD-DHJV</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>odchylka od ČR</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0.0339</v>
+      </c>
+      <c r="E38" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="F38" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="G38" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Síla = |hodnota / srovnání − 1|; u divergence pořadí |p1 − p2| / (počet území − 1). Rozdíly pod 3 % relativně se nehlásí. Položky struktury s podílem pod 5 % v území i v ČR se nehlásí. Popisy jsou věcné, bez interpretace.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Změna trendu se porovná se stejnou změnou všech ostatních oborů území (T30). Posunuly-li se stejným směrem, aspoň o 3 % relativně a aspoň o 50 % relativní změny oboru, jde o jev území, ne oboru: síla se sníží na vlastní část oboru |(1 + r oboru) / (1 + r ostatních oborů) − 1| a zjištění se ve shrnutí neuvádí jako zjištění oboru.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -10388,32 +11283,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ZJ_TYP</t>
+          <t>ZANIK_PO_ZPUSOB</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Typ zjištění</t>
+          <t>Zaniklé právnické osoby v oboru podle způsobu zániku (RES)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>zjisteni</t>
+          <t>pocet</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Odchylka od ČR, změna trendu, rozdíly uvnitř území, aktivita oboru vůči kraji, divergence pořadí.</t>
+          <t>PO zaniklé v roce, s převažující činností v oboru a sídlem v území, podle způsobu zániku ZPZAN (číselník RES 572) ve třech kategoriích – 04 zrušení bez likvidace bez nástupců, 01 likvidace, jiný způsob (přeměna 02, 03, ostatní a nezjištěné kódy).</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>report_zjisteni</t>
+          <t>count(subjekt PO) where year(ddatzan) = Y group by kategorie(zpzan)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>odvozeno z tabulek reportu</t>
+          <t>ČSÚ, RES – otevřená data</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -10423,12 +11318,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Dělení 04 / ostatní jen, jsou-li obě části aspoň na prahu; dělení ostatních na likvidaci a jiný způsob jen, jsou-li na prahu obě. Jinak pásmo podílu (PODIL_ZANIKU_04).</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Popis bez interpretace; „proč“ píše analytik.</t>
+          <t>Kód 04 zahrnuje i výmaz společnosti rejstříkovým soudem bez likvidace (§ 105a zákona č. 304/2013 Sb.); nárůst kódu 04 v celém území svědčí spíš o úklidu rejstříku než o zhoršení oboru.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -10445,32 +11340,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ZJ_SILA</t>
+          <t>PODIL_ZANIKU_04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Síla zjištění</t>
+          <t>Podíl zrušení bez likvidace bez nástupců (kód 04) na zaniklých PO v oboru (%)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>zjisteni</t>
+          <t>podil</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Absolutní relativní rozdíl |a / b − 1| (u divergence pořadí |p1 − p2| / (počet území − 1)).</t>
+          <t>Zaniklé PO s kódem 04 / všechny zaniklé PO oboru v roce × 100; když je jedna z částí pod prahem, uvádí se jen pásmo („aspoň X %“, „nejvýš X %“ v celých procentech).</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>report_zjisteni</t>
+          <t>100 × ZANIK_PO_ZPUSOB(04, Y) / ZANIK_PO_RES(Y)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>odvozeno ze zveřejněných čísel tabulek</t>
+          <t>odvozeno z RES</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -10480,12 +11375,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Zjištění pod 0,03 (3 %) se nehlásí.</t>
+          <t>Pásmo místo přesné hodnoty, je-li počet s kódem 04 nebo bez něj pod prahem; nic, jsou-li pod prahem obě části.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Bezrozměrné číslo, zjištění se podle něj řadí.</t>
+          <t>Odliší správní výmazy od zániků likvidací nebo přeměnou.</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -10502,32 +11397,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ZJ_HODNOTA</t>
+          <t>MIRA_ZANIKU_PO_BEZ04</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Hodnota zkoumaného území ve zjištění</t>
+          <t>Míra zániku právnických osob bez kódu 04 (%)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>zjisteni</t>
+          <t>podil</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Číslo z tabulky reportu, k níž zjištění odkazuje (nebo průměr čísel z ní).</t>
+          <t>Zaniklé PO v roce (nebo ve srovnatelném období) jiným způsobem než zrušením bez likvidace bez nástupců (ZPZAN 04) / stav PO k 1. 1. × 100; v řádcích „Ostatní obory“ za všechny ostatní obory území.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>report_zjisteni</t>
+          <t>100 × (ZANIK_PO_RES(Y) − ZANIK_PO_ZPUSOB(04, Y)) / ZANIK_PO_STAV(Y)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>tabulky reportu</t>
+          <t>odvozeno z RES</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -10537,12 +11432,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Je-li počet zániků bez kódu 04 pod prahem, jen pásmo „pod X %“ (X = práh / stav PO, zaokrouhleno nahoru na 0,1); je-li pod prahem počet s kódem 04, nic.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Míra zániku očištěná o správní výmazy; ukáže, zda obor zaniká i jinak než výmazem nečinných společností.</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -10559,32 +11454,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ZJ_SROVNANI</t>
+          <t>ZANIK_PO_STAV_OSTATNI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Srovnávací hodnota ve zjištění</t>
+          <t>Stav PO k 1. 1. – všechny ostatní obory území</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>zjisteni</t>
+          <t>pocet</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Číslo, s nímž se hodnota srovnává (ČR, kraj, předchozí roky – průměr, druhé pořadí).</t>
+          <t>Právnické osoby se sídlem v území a s určeným oborem (CZ-NACE 2025, automatické spojení, ne pseudokód) mimo zkoumaný obor, rekonstruované k 1. 1. stejně jako ZANIK_PO_STAV.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>report_zjisteni</t>
+          <t>count(PO ostatních oborů) where ddatvzn &lt; 1. 1. Y and (ddatzan is null or ddatzan &gt;= 1. 1. Y)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>tabulky reportu</t>
+          <t>ČSÚ, RES – otevřená data</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -10594,12 +11489,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Subjekty s neurčeným oborem a zařazené jen do vyšší úrovně se nezapočítávají ani do oboru, ani do ostatních oborů.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Jmenovatel míry zániku ostatních oborů (srovnání jevu oboru a jevu celého území).</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -10616,32 +11511,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ZJ_ROZDIL_PCT</t>
+          <t>MIRA_ZANIKU_PO_OSTATNI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Relativní rozdíl (%)</t>
+          <t>Míra zániku právnických osob ve všech ostatních oborech území (%)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>zjisteni</t>
+          <t>podil</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Absolutní hodnota 100 × (hodnota / srovnání − 1), zaokrouhleno na 0,1; směr (vyšší / nižší) je ve větě zjištění.</t>
+          <t>Zaniklé PO ostatních oborů v roce (nebo ve srovnatelném období; celkem nebo bez kódu 04) / stav PO ostatních oborů k 1. 1. × 100 – stejná metoda jako MIRA_ZANIKU_PO.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>report_zjisteni</t>
+          <t>100 × zaniklé PO ostatních oborů(Y) / ZANIK_PO_STAV_OSTATNI(Y)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>odvozeno</t>
+          <t>odvozeno z RES</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -10651,12 +11546,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>U divergence pořadí se neuvádí.</t>
+          <t>Stejná pravidla jako u míry zániku oboru.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Pod 3 % se rozdíl nehlásí a v textu se popisuje jako „srovnatelné“.</t>
+          <t>Posune-li se míra oboru stejně jako míra ostatních oborů území, jde o jev celého území, ne oboru (detektor zjištění).</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -10673,52 +11568,52 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MZDY_ZAM_OBOR</t>
+          <t>ZJ_JEV_UZEMI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Zaměstnanci v oboru a kraji (tis. osob, přepočtené počty)</t>
+          <t>Jev oboru, nebo celého území (zjištění změny trendu)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>kontext</t>
+          <t>zjisteni</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Průměrný evidenční počet zaměstnanců přepočtený na plný úvazek v sekci CZ-NACE oboru a v kraji (pracovištní metoda) nebo v ČR.</t>
+          <t>„území“ = ostatní obory území se posunuly stejným směrem a srovnatelně (relativní změna aspoň 3 % a aspoň polovina relativní změny oboru); „obor“ = neposunuly. Prázdné u zjištění, která se s ostatními obory neporovnávají.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>převzato (MZDCRRT2 kraje × sekce, MZDCRRT1 ČR × sekce; ukazatele 299AQ / 299A), zaokrouhleno na 0,1 tis.</t>
+          <t>r_ost × r_obor &gt; 0 and |r_ost| &gt;= 0,03 and |r_ost| &gt;= 0,5 × |r_obor|</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ČSÚ, DataStat, roční zjišťování (sada MZDCRR)</t>
+          <t>odvozeno z T18 a T30</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>CR, kraj</t>
+          <t>CR, kraj, okres</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Jen jednotlivé sekce CZ-NACE (oddíl a nižší úrovně → sekce s označením); okresy ČSÚ nepublikuje (→ kraj s označením); kraj × sekce jen 2010–2022 (2022 předběžně).</t>
+          <t>Jen u zjištění typu změna trendu, má-li srovnání ostatních oborů zveřejněné hodnoty.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Zaměstnanci v pracovním poměru, ne podnikající fyzické osoby; nesrovnává se s počtem registrovaných subjektů.</t>
+          <t>Zjištění s příznakem „území“ má sníženou sílu (vlastní část oboru) a ve shrnutí se neuvádí jako zjištění oboru.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>částečně</t>
+          <t>naplněno</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -10730,52 +11625,52 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MZDY_ZAM_PODIL_CR</t>
+          <t>ZJ_TYP</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Podíl kraje na zaměstnancích oboru v ČR (%)</t>
+          <t>Typ zjištění</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>podil</t>
+          <t>zjisteni</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Zaměstnanci oboru v kraji / zaměstnanci oboru v ČR × 100, obojí z ročního zjišťování.</t>
+          <t>Odchylka od ČR, změna trendu, rozdíly uvnitř území, aktivita oboru vůči kraji, divergence pořadí.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>100 × MZDY_ZAM_OBOR(kraj) / MZDY_ZAM_OBOR(ČR)</t>
+          <t>report_zjisteni</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>odvozeno z publikovaných údajů ČSÚ (MZDCRR)</t>
+          <t>odvozeno z tabulek reportu</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>kraj</t>
+          <t>CR, kraj, okres</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Jen jsou-li publikovány oba údaje.</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Srovnávejte s podílem kraje na registrovaných subjektech oboru (REG_PODIL_CR).</t>
+          <t>Popis bez interpretace; „proč“ píše analytik.</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>částečně</t>
+          <t>naplněno</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -10787,52 +11682,52 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MZDY_ZAM_PODIL_UZEMI</t>
+          <t>ZJ_SILA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Podíl oboru na zaměstnancích území (%)</t>
+          <t>Síla zjištění</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>podil</t>
+          <t>zjisteni</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Zaměstnanci oboru / zaměstnanci všech odvětví v témže území × 100.</t>
+          <t>Absolutní relativní rozdíl |a / b − 1| (u divergence pořadí |p1 − p2| / (počet území − 1)).</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>100 × MZDY_ZAM_OBOR / zaměstnanci celkem (sekce „Celkem“)</t>
+          <t>report_zjisteni</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>odvozeno z publikovaných údajů ČSÚ (MZDCRR)</t>
+          <t>odvozeno ze zveřejněných čísel tabulek</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>CR, kraj</t>
+          <t>CR, kraj, okres</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Jen jsou-li publikovány oba údaje.</t>
+          <t>Zjištění pod 0,03 (3 %) se nehlásí.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Váha oboru na trhu práce území; srovnání kraje s ČR ukazuje specializaci podle zaměstnanosti.</t>
+          <t>Bezrozměrné číslo, zjištění se podle něj řadí.</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>částečně</t>
+          <t>naplněno</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -10844,52 +11739,52 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MZDY_MZDA_OBOR</t>
+          <t>ZJ_HODNOTA</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Průměrná hrubá měsíční mzda v oboru a kraji (Kč)</t>
+          <t>Hodnota zkoumaného území ve zjištění</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>kontext</t>
+          <t>zjisteni</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Průměrná hrubá měsíční mzda na přepočtené počty zaměstnanců v sekci CZ-NACE oboru a v kraji nebo v ČR.</t>
+          <t>Číslo z tabulky reportu, k níž zjištění odkazuje (nebo průměr čísel z ní).</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>převzato (MZDCRRT2, MZDCRRT1; ukazatel 5958P), zaokrouhleno na celé Kč</t>
+          <t>report_zjisteni</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>ČSÚ, DataStat, roční zjišťování (sada MZDCRR)</t>
+          <t>tabulky reportu</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>CR, kraj</t>
+          <t>CR, kraj, okres</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Jako MZDY_ZAM_OBOR. Medián za kraj × odvětví ČSÚ nepublikuje (za kraje jen podle pohlaví).</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Průměr je citlivý na vysoké mzdy; medián pro kraj × odvětví není k dispozici.</t>
+          <t>–</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>částečně</t>
+          <t>naplněno</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -10901,52 +11796,52 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MZDY_MZDA_INDEX_CR</t>
+          <t>ZJ_SROVNANI</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mzda v oboru a kraji proti oboru v ČR (ČR = 100)</t>
+          <t>Srovnávací hodnota ve zjištění</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>index</t>
+          <t>zjisteni</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Průměrná mzda oboru v kraji / průměrná mzda oboru v ČR × 100.</t>
+          <t>Číslo, s nímž se hodnota srovnává (ČR, kraj, předchozí roky – průměr, druhé pořadí).</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>100 × MZDY_MZDA_OBOR(kraj) / MZDY_MZDA_OBOR(ČR)</t>
+          <t>report_zjisteni</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>odvozeno z publikovaných údajů ČSÚ (MZDCRR)</t>
+          <t>tabulky reportu</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>kraj</t>
+          <t>CR, kraj, okres</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Jen jsou-li publikovány oba údaje.</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Pod 100 = obor v kraji platí méně než obor v ČR.</t>
+          <t>–</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>částečně</t>
+          <t>naplněno</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -10958,52 +11853,52 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MZDY_MZDA_INDEX_UZEMI</t>
+          <t>ZJ_ROZDIL_PCT</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Mzda v oboru proti všem odvětvím území (= 100)</t>
+          <t>Relativní rozdíl (%)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>index</t>
+          <t>zjisteni</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Průměrná mzda oboru / průměrná mzda všech odvětví v témže území × 100.</t>
+          <t>Absolutní hodnota 100 × (hodnota / srovnání − 1), zaokrouhleno na 0,1; směr (vyšší / nižší) je ve větě zjištění.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>100 × MZDY_MZDA_OBOR / mzda celkem (sekce „Celkem“)</t>
+          <t>report_zjisteni</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>odvozeno z publikovaných údajů ČSÚ (MZDCRR)</t>
+          <t>odvozeno</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>CR, kraj</t>
+          <t>CR, kraj, okres</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Jen jsou-li publikovány oba údaje.</t>
+          <t>U divergence pořadí se neuvádí.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Postavení oboru mezi odvětvími téhož území.</t>
+          <t>Pod 3 % se rozdíl nehlásí a v textu se popisuje jako „srovnatelné“.</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>částečně</t>
+          <t>naplněno</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -11015,12 +11910,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MZDY_ZAM_UROVEN</t>
+          <t>MZDY_ZAM_OBOR</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Zaměstnanci v nejbližší publikované úrovni (tis. osob, přepočtené počty)</t>
+          <t>Zaměstnanci v oboru a kraji (tis. osob, přepočtené počty)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -11030,17 +11925,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Kraj za všechna odvětví nebo ČR za sekci oboru – pro roky, za které ČSÚ obor × kraj nepublikuje.</t>
+          <t>Průměrný evidenční počet zaměstnanců přepočtený na plný úvazek v sekci CZ-NACE oboru a v kraji (pracovištní metoda) nebo v ČR.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>převzato (MZDRT5, MZDRT2; ukazatel 299A), zaokrouhleno na 0,1 tis.</t>
+          <t>převzato (MZDCRRT2 kraje × sekce, MZDCRRT1 ČR × sekce; ukazatele 299AQ / 299A), zaokrouhleno na 0,1 tis.</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>ČSÚ, DataStat, čtvrtletní zjišťování (sada MZDR), kumulace za rok</t>
+          <t>ČSÚ, DataStat, roční zjišťování (sada MZDCRR)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -11050,12 +11945,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Kraj × odvětví čtvrtletní zjišťování nepublikuje.</t>
+          <t>Jen jednotlivé sekce CZ-NACE (oddíl a nižší úrovně → sekce s označením); okresy ČSÚ nepublikuje (→ kraj s označením); kraj × sekce jen 2010–2022 (2022 předběžně).</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Jiné zjišťování než MZDY_ZAM_OBOR; řady se nespojují.</t>
+          <t>Zaměstnanci v pracovním poměru, ne podnikající fyzické osoby; nesrovnává se s počtem registrovaných subjektů.</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -11072,47 +11967,47 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MZDY_MZDA_UROVEN</t>
+          <t>MZDY_ZAM_PODIL_CR</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Průměrná mzda v nejbližší publikované úrovni (Kč)</t>
+          <t>Podíl kraje na zaměstnancích oboru v ČR (%)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>kontext</t>
+          <t>podil</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Kraj za všechna odvětví nebo ČR za sekci oboru – pro roky, za které ČSÚ obor × kraj nepublikuje.</t>
+          <t>Zaměstnanci oboru v kraji / zaměstnanci oboru v ČR × 100, obojí z ročního zjišťování.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>převzato (MZDRT5, MZDRT2; ukazatel 5958P), zaokrouhleno na celé Kč</t>
+          <t>100 × MZDY_ZAM_OBOR(kraj) / MZDY_ZAM_OBOR(ČR)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>ČSÚ, DataStat, čtvrtletní zjišťování (sada MZDR), kumulace za rok</t>
+          <t>odvozeno z publikovaných údajů ČSÚ (MZDCRR)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>CR, kraj</t>
+          <t>kraj</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Kraj × odvětví čtvrtletní zjišťování nepublikuje.</t>
+          <t>Jen jsou-li publikovány oba údaje.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Jiné zjišťování než MZDY_MZDA_OBOR; řady se nespojují.</t>
+          <t>Srovnávejte s podílem kraje na registrovaných subjektech oboru (REG_PODIL_CR).</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -11129,32 +12024,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>EKON_HPH</t>
+          <t>MZDY_ZAM_PODIL_UZEMI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Hrubá přidaná hodnota skupiny odvětví (mil. Kč, běžné ceny)</t>
+          <t>Podíl oboru na zaměstnancích území (%)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>kontext</t>
+          <t>podil</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Hrubá přidaná hodnota v základních cenách ve skupině odvětví A*10, do níž patří obor, v kraji, regionu soudržnosti nebo ČR.</t>
+          <t>Zaměstnanci oboru / zaměstnanci všech odvětví v témže území × 100.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>převzato (Eurostat nama_10r_3gva, unit CP_MNAC), zaokrouhleno na celé mil. Kč</t>
+          <t>100 × MZDY_ZAM_OBOR / zaměstnanci celkem (sekce „Celkem“)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Eurostat, regionální účty (nama_10r_3gva)</t>
+          <t>odvozeno z publikovaných údajů ČSÚ (MZDCRR)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -11164,12 +12059,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Jen skupiny A*10 (oddíl a nižší úrovně → skupina s označením; B, D, E → B–E; G, H, I → G–I; M, N → M–N; O–Q; R–U); okresy neexistují (→ kraj s označením).</t>
+          <t>Jen jsou-li publikovány oba údaje.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Přidaná hodnota podle místa pracoviště jednotek, ne podle sídla subjektu.</t>
+          <t>Váha oboru na trhu práce území; srovnání kraje s ČR ukazuje specializaci podle zaměstnanosti.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -11186,32 +12081,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>EKON_HPH_PODIL_UZEMI</t>
+          <t>MZDY_MZDA_OBOR</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Podíl skupiny odvětví na HPH území (%)</t>
+          <t>Průměrná hrubá měsíční mzda v oboru a kraji (Kč)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>podil</t>
+          <t>kontext</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>HPH skupiny / HPH všech odvětví téhož území a roku × 100.</t>
+          <t>Průměrná hrubá měsíční mzda na přepočtené počty zaměstnanců v sekci CZ-NACE oboru a v kraji nebo v ČR.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>100 × EKON_HPH / HPH TOTAL</t>
+          <t>převzato (MZDCRRT2, MZDCRRT1; ukazatel 5958P), zaokrouhleno na celé Kč</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>odvozeno z Eurostatu (nama_10r_3gva)</t>
+          <t>ČSÚ, DataStat, roční zjišťování (sada MZDCRR)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -11221,12 +12116,12 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Jen jsou-li publikovány oba údaje.</t>
+          <t>Jako MZDY_ZAM_OBOR. Medián za kraj × odvětví ČSÚ nepublikuje (za kraje jen podle pohlaví).</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Váha oboru v ekonomice území; srovnání kraje s ČR ukazuje specializaci podle přidané hodnoty.</t>
+          <t>Průměr je citlivý na vysoké mzdy; medián pro kraj × odvětví není k dispozici.</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -11243,32 +12138,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>EKON_HPH_PODIL_CR</t>
+          <t>MZDY_MZDA_INDEX_CR</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Podíl kraje na HPH skupiny odvětví v ČR (%)</t>
+          <t>Mzda v oboru a kraji proti oboru v ČR (ČR = 100)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>podil</t>
+          <t>index</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>HPH skupiny v kraji / HPH skupiny v ČR × 100.</t>
+          <t>Průměrná mzda oboru v kraji / průměrná mzda oboru v ČR × 100.</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>100 × EKON_HPH(kraj) / EKON_HPH(ČR)</t>
+          <t>100 × MZDY_MZDA_OBOR(kraj) / MZDY_MZDA_OBOR(ČR)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>odvozeno z Eurostatu (nama_10r_3gva)</t>
+          <t>odvozeno z publikovaných údajů ČSÚ (MZDCRR)</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -11283,7 +12178,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Srovnávejte s podílem kraje na registrovaných subjektech oboru (REG_PODIL_CR).</t>
+          <t>Pod 100 = obor v kraji platí méně než obor v ČR.</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -11300,12 +12195,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>EKON_HPH_RUST</t>
+          <t>MZDY_MZDA_INDEX_UZEMI</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Objemová změna HPH proti předchozímu roku (%)</t>
+          <t>Mzda v oboru proti všem odvětvím území (= 100)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -11315,17 +12210,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>HPH v cenách předchozího roku / HPH v běžných cenách předchozího roku − 1, × 100.</t>
+          <t>Průměrná mzda oboru / průměrná mzda všech odvětví v témže území × 100.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>100 × (HPH_PYP(t) / HPH_CP(t−1) − 1)</t>
+          <t>100 × MZDY_MZDA_OBOR / mzda celkem (sekce „Celkem“)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>odvozeno z Eurostatu (nama_10r_3gva, unit PYP_MNAC a CP_MNAC)</t>
+          <t>odvozeno z publikovaných údajů ČSÚ (MZDCRR)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -11340,7 +12235,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Reálná (objemová) změna bez vlivu cen.</t>
+          <t>Postavení oboru mezi odvětvími téhož území.</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -11357,32 +12252,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>EKON_HPH_OBJEM_INDEX</t>
+          <t>MZDY_ZAM_UROVEN</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Objem HPH (první rok tabulky = 100)</t>
+          <t>Zaměstnanci v nejbližší publikované úrovni (tis. osob, přepočtené počty)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>index</t>
+          <t>kontext</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Řetězení meziročních objemových změn HPH od prvního roku tabulky.</t>
+          <t>Kraj za všechna odvětví nebo ČR za sekci oboru – pro roky, za které ČSÚ obor × kraj nepublikuje.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>100 × Π (HPH_PYP(t) / HPH_CP(t−1))</t>
+          <t>převzato (MZDRT5, MZDRT2; ukazatel 299A), zaokrouhleno na 0,1 tis.</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>odvozeno z Eurostatu (nama_10r_3gva)</t>
+          <t>ČSÚ, DataStat, čtvrtletní zjišťování (sada MZDR), kumulace za rok</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -11392,12 +12287,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Jen jsou-li publikovány všechny roky.</t>
+          <t>Kraj × odvětví čtvrtletní zjišťování nepublikuje.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Reálný vývoj za celé období tabulky.</t>
+          <t>Jiné zjišťování než MZDY_ZAM_OBOR; řady se nespojují.</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -11414,12 +12309,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>EKON_ZAM</t>
+          <t>MZDY_MZDA_UROVEN</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Zaměstnaní ve skupině odvětví (tis. osob, národní účty)</t>
+          <t>Průměrná mzda v nejbližší publikované úrovni (Kč)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -11429,17 +12324,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Zaměstnanost podle národních účtů – zaměstnanci i sebezaměstnaní (včetně podnikajících fyzických osob), podle místa pracoviště.</t>
+          <t>Kraj za všechna odvětví nebo ČR za sekci oboru – pro roky, za které ČSÚ obor × kraj nepublikuje.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>převzato (Eurostat nama_10r_3empers, wstatus EMP)</t>
+          <t>převzato (MZDRT5, MZDRT2; ukazatel 5958P), zaokrouhleno na celé Kč</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Eurostat, regionální účty (nama_10r_3empers)</t>
+          <t>ČSÚ, DataStat, čtvrtletní zjišťování (sada MZDR), kumulace za rok</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -11449,12 +12344,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Jako EKON_HPH.</t>
+          <t>Kraj × odvětví čtvrtletní zjišťování nepublikuje.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Liší se od přepočtených zaměstnanců ČSÚ (MZDY_ZAM_OBOR) – zahrnuje sebezaměstnané a počítá osoby, ne plné úvazky.</t>
+          <t>Jiné zjišťování než MZDY_MZDA_OBOR; řady se nespojují.</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -11471,32 +12366,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>EKON_ZAM_PODIL_SELF</t>
+          <t>EKON_HPH</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Podíl sebezaměstnaných na zaměstnaných (%)</t>
+          <t>Hrubá přidaná hodnota skupiny odvětví (mil. Kč, běžné ceny)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>podil</t>
+          <t>kontext</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Sebezaměstnaní / zaměstnaní celkem × 100 (národní účty).</t>
+          <t>Hrubá přidaná hodnota v základních cenách ve skupině odvětví A*10, do níž patří obor, v kraji, regionu soudržnosti nebo ČR.</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>100 × ZAM_SELF / ZAM_EMP</t>
+          <t>převzato (Eurostat nama_10r_3gva, unit CP_MNAC), zaokrouhleno na celé mil. Kč</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>odvozeno z Eurostatu (nama_10r_3empers)</t>
+          <t>Eurostat, regionální účty (nama_10r_3gva)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -11506,12 +12401,12 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Jen jsou-li publikovány oba údaje.</t>
+          <t>Jen skupiny A*10 (oddíl a nižší úrovně → skupina s označením; B, D, E → B–E; G, H, I → G–I; M, N → M–N; O–Q; R–U); okresy neexistují (→ kraj s označením).</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Váha samostatně podnikajících v pracovní síle oboru.</t>
+          <t>Přidaná hodnota podle místa pracoviště jednotek, ne podle sídla subjektu.</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -11528,32 +12423,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>EKON_PRODUKTIVITA</t>
+          <t>EKON_HPH_PODIL_UZEMI</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Hrubá přidaná hodnota na zaměstnaného (tis. Kč)</t>
+          <t>Podíl skupiny odvětví na HPH území (%)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>index</t>
+          <t>podil</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>HPH v běžných cenách / zaměstnaní (obojí Eurostat, regionální účty), zaokrouhleno na celé tis. Kč.</t>
+          <t>HPH skupiny / HPH všech odvětví téhož území a roku × 100.</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>EKON_HPH / EKON_ZAM (mil. Kč / tis. osob = tis. Kč)</t>
+          <t>100 × EKON_HPH / HPH TOTAL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>odvozeno z Eurostatu (nama_10r_3gva, nama_10r_3empers)</t>
+          <t>odvozeno z Eurostatu (nama_10r_3gva)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -11568,7 +12463,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Nominální produktivita na osobu (ne na odpracovanou hodinu).</t>
+          <t>Váha oboru v ekonomice území; srovnání kraje s ČR ukazuje specializaci podle přidané hodnoty.</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -11585,32 +12480,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>EKON_PRODUKTIVITA_INDEX_CR</t>
+          <t>EKON_HPH_PODIL_CR</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Produktivita proti ČR (ČR = 100)</t>
+          <t>Podíl kraje na HPH skupiny odvětví v ČR (%)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>index</t>
+          <t>podil</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Produktivita skupiny v kraji / produktivita skupiny v ČR × 100.</t>
+          <t>HPH skupiny v kraji / HPH skupiny v ČR × 100.</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>100 × EKON_PRODUKTIVITA(kraj) / EKON_PRODUKTIVITA(ČR)</t>
+          <t>100 × EKON_HPH(kraj) / EKON_HPH(ČR)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>odvozeno z Eurostatu</t>
+          <t>odvozeno z Eurostatu (nama_10r_3gva)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -11620,12 +12515,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Jen jsou-li publikovány všechny údaje.</t>
+          <t>Jen jsou-li publikovány oba údaje.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Pod 100 = nižší přidaná hodnota na zaměstnaného než v oboru v ČR.</t>
+          <t>Srovnávejte s podílem kraje na registrovaných subjektech oboru (REG_PODIL_CR).</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -11642,47 +12537,47 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>EKON_NAHRADY</t>
+          <t>EKON_HPH_RUST</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Náhrady zaměstnancům ve skupině odvětví (mil. Kč)</t>
+          <t>Objemová změna HPH proti předchozímu roku (%)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>kontext</t>
+          <t>index</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Mzdy a platy a sociální příspěvky zaměstnavatelů ve skupině A*10, region soudržnosti nebo ČR.</t>
+          <t>HPH v cenách předchozího roku / HPH v běžných cenách předchozího roku − 1, × 100.</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>převzato (Eurostat nama_10r_2coe, currency MIO_NAC)</t>
+          <t>100 × (HPH_PYP(t) / HPH_CP(t−1) − 1)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Eurostat, regionální účty (nama_10r_2coe)</t>
+          <t>odvozeno z Eurostatu (nama_10r_3gva, unit PYP_MNAC a CP_MNAC)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>CR, region soudržnosti</t>
+          <t>CR, kraj</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Za kraje Eurostat nepublikuje – uvádí se region soudržnosti (NUTS 2) s označením.</t>
+          <t>Jen jsou-li publikovány oba údaje.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Region zahrnuje více krajů.</t>
+          <t>Reálná (objemová) změna bez vlivu cen.</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -11699,47 +12594,47 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>EKON_NAHRADY_PODIL</t>
+          <t>EKON_HPH_OBJEM_INDEX</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Podíl náhrad zaměstnancům na HPH (%)</t>
+          <t>Objem HPH (první rok tabulky = 100)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>podil</t>
+          <t>index</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Náhrady zaměstnancům / HPH v běžných cenách × 100, týž region a rok.</t>
+          <t>Řetězení meziročních objemových změn HPH od prvního roku tabulky.</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>100 × EKON_NAHRADY / EKON_HPH (NUTS 2)</t>
+          <t>100 × Π (HPH_PYP(t) / HPH_CP(t−1))</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>odvozeno z Eurostatu (nama_10r_2coe, nama_10r_3gva)</t>
+          <t>odvozeno z Eurostatu (nama_10r_3gva)</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>CR, region soudržnosti</t>
+          <t>CR, kraj</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Jen region soudržnosti a ČR.</t>
+          <t>Jen jsou-li publikovány všechny roky.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Nízký podíl = větší část přidané hodnoty připadá na provozní přebytek a příjmy podnikatelů.</t>
+          <t>Reálný vývoj za celé období tabulky.</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -11756,32 +12651,32 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MODEL_HPH</t>
+          <t>EKON_ZAM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Přidaná hodnota oboru v kraji podle velikostní třídy (mil. Kč, modelový odhad)</t>
+          <t>Zaměstnaní ve skupině odvětví (tis. osob, národní účty)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>odhad</t>
+          <t>kontext</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Krajská přidaná hodnota skupiny (Eurostat, regionální účty) přepočtená na úroveň statistiky podniků (MODEL_POMER_SBS) a rozpočítaná mezi třídy podle počtu subjektů (RES, KATPO, podíl se zjištěnou aktivitou podle ČSÚ) × celostátní přidané hodnoty na podnik třídy (Eurostat SBS).</t>
+          <t>Zaměstnanost podle národních účtů – zaměstnanci i sebezaměstnaní (včetně podnikajících fyzických osob), podle místa pracoviště.</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>HPH_kraj × MODEL_POMER_SBS × n(c)·AV(c)/ENT(c) / Σ n·AV/ENT; pásmo podle zařazení KATPO „Neuvedeno“</t>
+          <t>převzato (Eurostat nama_10r_3empers, wstatus EMP)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>modelový odhad (RES, ČSÚ RES02QNACET1, Eurostat nama_10r_3gva, sbs_sc_ovw přes sekce Rev. 2)</t>
+          <t>Eurostat, regionální účty (nama_10r_3empers)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -11791,12 +12686,12 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Jen obor = celá sekce, která je samostatnou skupinou A*10; třídy pod prahem 10 subjektů sloučeny.</t>
+          <t>Jako EKON_HPH.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Modelový odhad, ne statistika. Součet tříd = krajský fakt.</t>
+          <t>Liší se od přepočtených zaměstnanců ČSÚ (MZDY_ZAM_OBOR) – zahrnuje sebezaměstnané a počítá osoby, ne plné úvazky.</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -11813,32 +12708,32 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MODEL_HPH_PODIL</t>
+          <t>EKON_ZAM_PODIL_SELF</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Podíl velikostní třídy na přidané hodnotě oboru v kraji (%, modelový odhad)</t>
+          <t>Podíl sebezaměstnaných na zaměstnaných (%)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>odhad</t>
+          <t>podil</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>MODEL_HPH třídy / přidaná hodnota skupiny v kraji × 100.</t>
+          <t>Sebezaměstnaní / zaměstnaní celkem × 100 (národní účty).</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>100 × MODEL_HPH / EKON_HPH</t>
+          <t>100 × ZAM_SELF / ZAM_EMP</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>modelový odhad</t>
+          <t>odvozeno z Eurostatu (nama_10r_3empers)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -11848,12 +12743,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Jako MODEL_HPH.</t>
+          <t>Jen jsou-li publikovány oba údaje.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Modelový odhad.</t>
+          <t>Váha samostatně podnikajících v pracovní síle oboru.</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -11870,32 +12765,32 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MODEL_OBRAT</t>
+          <t>EKON_PRODUKTIVITA</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Obrat oboru v kraji (mil. Kč, modelový odhad)</t>
+          <t>Hrubá přidaná hodnota na zaměstnaného (tis. Kč)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>odhad</t>
+          <t>index</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>MODEL_HPH třídy × celostátní poměr čistého obratu k přidané hodnotě v třídě (SBS).</t>
+          <t>HPH v běžných cenách / zaměstnaní (obojí Eurostat, regionální účty), zaokrouhleno na celé tis. Kč.</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Σ MODEL_HPH(c) × NETTUR(c)/AV(c)</t>
+          <t>EKON_HPH / EKON_ZAM (mil. Kč / tis. osob = tis. Kč)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>modelový odhad</t>
+          <t>odvozeno z Eurostatu (nama_10r_3gva, nama_10r_3empers)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -11905,12 +12800,12 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Jako MODEL_HPH.</t>
+          <t>Jen jsou-li publikovány oba údaje.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Vychází z přidané hodnoty přepočtené na úroveň SBS; kontrola na ČR viz MODEL_KONTROLA.</t>
+          <t>Nominální produktivita na osobu (ne na odpracovanou hodinu).</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -11927,47 +12822,47 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MODEL_KONCENTRACE</t>
+          <t>EKON_PRODUKTIVITA_INDEX_CR</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Podíl subjektů s 10+ a 50+ zaměstnanými osobami na přidané hodnotě a obratu (%, modelový odhad)</t>
+          <t>Produktivita proti ČR (ČR = 100)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>odhad</t>
+          <t>index</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Součet MODEL_HPH, resp. MODEL_OBRAT tříd nad hranicí / celek × 100.</t>
+          <t>Produktivita skupiny v kraji / produktivita skupiny v ČR × 100.</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>100 × Σ_{c ≥ hranice} MODEL_HPH(c) / Σ MODEL_HPH</t>
+          <t>100 × EKON_PRODUKTIVITA(kraj) / EKON_PRODUKTIVITA(ČR)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>modelový odhad</t>
+          <t>odvozeno z Eurostatu</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>CR, kraj</t>
+          <t>kraj</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Nezveřejní se, pokud by hranice rozdělila sloučenou třídu pod prahem.</t>
+          <t>Jen jsou-li publikovány všechny údaje.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Koncentrace podle tříd, ne podle jednotlivých subjektů.</t>
+          <t>Pod 100 = nižší přidaná hodnota na zaměstnaného než v oboru v ČR.</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -11984,52 +12879,52 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MODEL_KONTROLA</t>
+          <t>EKON_NAHRADY</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Kontrola konzistence modelu na celé ČR</t>
+          <t>Náhrady zaměstnancům ve skupině odvětví (mil. Kč)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>odhad</t>
+          <t>kontext</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Model se stejnými vstupy za celou ČR proti hodnotám SBS; odchylka v p. b. (podíly) nebo % (obrat).</t>
+          <t>Mzdy a platy a sociální příspěvky zaměstnavatelů ve skupině A*10, region soudržnosti nebo ČR.</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>report.tabulky_model</t>
+          <t>převzato (Eurostat nama_10r_2coe, currency MIO_NAC)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>modelový odhad a Eurostat SBS</t>
+          <t>Eurostat, regionální účty (nama_10r_2coe)</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>CR, region soudržnosti</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Za kraje Eurostat nepublikuje – uvádí se region soudržnosti (NUTS 2) s označením.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Ukazuje přesnost modelu tam, kde fakt známe.</t>
+          <t>Region zahrnuje více krajů.</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>naplněno</t>
+          <t>částečně</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -12041,52 +12936,52 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SBS_PODNIKY</t>
+          <t>EKON_NAHRADY_PODIL</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Počet podniků v ČR podle velikostní třídy (Eurostat SBS)</t>
+          <t>Podíl náhrad zaměstnancům na HPH (%)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>kontext</t>
+          <t>podil</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Aktivní podniky v sekci za ČR, třída podle počtu zaměstnaných osob.</t>
+          <t>Náhrady zaměstnancům / HPH v běžných cenách × 100, týž region a rok.</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>převzato (sbs_sc_ovw, ENT_NR)</t>
+          <t>100 × EKON_NAHRADY / EKON_HPH (NUTS 2)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Eurostat, sbs_sc_ovw</t>
+          <t>odvozeno z Eurostatu (nama_10r_2coe, nama_10r_3gva)</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>CR, region soudržnosti</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Jen region soudržnosti a ČR.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Podniky, ne registrované subjekty.</t>
+          <t>Nízký podíl = větší část přidané hodnoty připadá na provozní přebytek a příjmy podnikatelů.</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>naplněno</t>
+          <t>částečně</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -12098,52 +12993,52 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SBS_OSOBY</t>
+          <t>MODEL_HPH</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Zaměstnané osoby v ČR podle velikostní třídy (Eurostat SBS)</t>
+          <t>Přidaná hodnota oboru v kraji podle velikostní třídy (mil. Kč, modelový odhad)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>kontext</t>
+          <t>odhad</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Zaměstnané osoby včetně majitelů a spolupracujících osob.</t>
+          <t>Krajská přidaná hodnota skupiny (Eurostat, regionální účty) přepočtená na úroveň statistiky podniků (MODEL_POMER_SBS) a rozpočítaná mezi třídy podle počtu subjektů (RES, KATPO, podíl se zjištěnou aktivitou podle ČSÚ) × celostátní přidané hodnoty na podnik třídy (Eurostat SBS).</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>převzato (sbs_sc_ovw, EMP_NR)</t>
+          <t>HPH_kraj × MODEL_POMER_SBS × n(c)·AV(c)/ENT(c) / Σ n·AV/ENT; pásmo podle zařazení KATPO „Neuvedeno“</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Eurostat, sbs_sc_ovw</t>
+          <t>modelový odhad (RES, ČSÚ RES02QNACET1, Eurostat nama_10r_3gva, sbs_sc_ovw přes sekce Rev. 2)</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>CR, kraj</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Jen obor = celá sekce, která je samostatnou skupinou A*10; třídy pod prahem 10 subjektů sloučeny.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Modelový odhad, ne statistika. Součet tříd = krajský fakt.</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>naplněno</t>
+          <t>částečně</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -12155,52 +13050,52 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SBS_OBRAT_PODNIK</t>
+          <t>MODEL_HPH_PODIL</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Průměrný obrat podniku v ČR podle velikostní třídy (mil. Kč)</t>
+          <t>Podíl velikostní třídy na přidané hodnotě oboru v kraji (%, modelový odhad)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>kontext</t>
+          <t>odhad</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Čistý obrat / počet podniků, převedeno ročním průměrným kurzem CZK/EUR; pásmo min.–max. mezi oddíly sekce.</t>
+          <t>MODEL_HPH třídy / přidaná hodnota skupiny v kraji × 100.</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>NETTUR_MEUR / ENT_NR × kurz</t>
+          <t>100 × MODEL_HPH / EKON_HPH</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Eurostat, sbs_sc_ovw, ert_bil_eur_a</t>
+          <t>modelový odhad</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>CR, kraj</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Peněžní údaje jen za třídy 0–9, 10–19, 20–49, 50–249, 250+.</t>
+          <t>Jako MODEL_HPH.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Průměr, ne medián; fakt za ČR.</t>
+          <t>Modelový odhad.</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>naplněno</t>
+          <t>částečně</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -12212,52 +13107,52 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SBS_MARZE</t>
+          <t>MODEL_OBRAT</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Hrubý provozní přebytek / obrat v ČR podle velikostní třídy (%)</t>
+          <t>Obrat oboru v kraji (mil. Kč, modelový odhad)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>kontext</t>
+          <t>odhad</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Hrubý provozní přebytek / čistý obrat × 100, za ČR.</t>
+          <t>MODEL_HPH třídy × celostátní poměr čistého obratu k přidané hodnotě v třídě (SBS).</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>100 × GOS_MEUR / NETTUR_MEUR</t>
+          <t>Σ MODEL_HPH(c) × NETTUR(c)/AV(c)</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Eurostat, sbs_sc_ovw</t>
+          <t>modelový odhad</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>CR, kraj</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Jako MODEL_HPH.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Fakt za ČR, ne odhad za kraj; hrubý provozní přebytek zahrnuje i odměnu podnikatelů bez zaměstnanců.</t>
+          <t>Vychází z přidané hodnoty přepočtené na úroveň SBS; kontrola na ČR viz MODEL_KONTROLA.</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>naplněno</t>
+          <t>částečně</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -12269,12 +13164,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>MODEL_POMER_SBS</t>
+          <t>MODEL_KONCENTRACE</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Poměr přidané hodnoty SBS a národních účtů za ČR (týž obor a rok)</t>
+          <t>Podíl subjektů s 10+ a 50+ zaměstnanými osobami na přidané hodnotě a obratu (%, modelový odhad)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -12284,37 +13179,37 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Přidaná hodnota sekce za ČR ze statistiky podniků (SBS, v Kč) / přidaná hodnota téže sekce za ČR z národních (regionálních) účtů.</t>
+          <t>Součet MODEL_HPH, resp. MODEL_OBRAT tříd nad hranicí / celek × 100.</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AV_MEUR(ČR) × kurz / HPH_CP(ČR)</t>
+          <t>100 × Σ_{c ≥ hranice} MODEL_HPH(c) / Σ MODEL_HPH</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>odvozeno z Eurostatu (sbs_sc_ovw, ert_bil_eur_a, nama_10r_3gva)</t>
+          <t>modelový odhad</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>CR, kraj</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Jen jsou-li publikovány obě hodnoty pro týž rok.</t>
+          <t>Nezveřejní se, pokud by hranice rozdělila sloučenou třídu pod prahem.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Měřítko přepočtu krajské přidané hodnoty pro model (rozhodnutí 14); předpokládá stejný podíl neregistrované ekonomiky v kraji jako v ČR.</t>
+          <t>Koncentrace podle tříd, ne podle jednotlivých subjektů.</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>naplněno</t>
+          <t>částečně</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -12326,55 +13221,112 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SBS_HPH</t>
+          <t>MODEL_KONTROLA</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Přidaná hodnota sekce za ČR podle statistiky podniků (mil. Kč)</t>
+          <t>Kontrola konzistence modelu na celé ČR</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
+          <t>odhad</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Model se stejnými vstupy za celou ČR proti hodnotám SBS; odchylka v p. b. (podíly) nebo % (obrat).</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>report.tabulky_model</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>modelový odhad a Eurostat SBS</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Ukazuje přesnost modelu tam, kde fakt známe.</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>SBS_PODNIKY</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Počet podniků v ČR podle velikostní třídy (Eurostat SBS)</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
           <t>kontext</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Přidaná hodnota v nákladech na výrobní činitele (SBS), mil. EUR převedené ročním průměrným kurzem.</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AV_MEUR × kurz</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Eurostat, sbs_sc_ovw, ert_bil_eur_a</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Aktivní podniky v sekci za ČR, třída podle počtu zaměstnaných osob.</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>převzato (sbs_sc_ovw, ENT_NR)</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Eurostat, sbs_sc_ovw</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
         <is>
           <t>CR</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>Nižší než přidaná hodnota národních účtů (bez neregistrované ekonomiky, jiné ocenění).</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Podniky, ne registrované subjekty.</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
         <is>
           <t>naplněno</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="K77" t="inlineStr">
         <is>
           <t>ano</t>
         </is>
@@ -12382,6 +13334,291 @@
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
+        <is>
+          <t>SBS_OSOBY</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Zaměstnané osoby v ČR podle velikostní třídy (Eurostat SBS)</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>kontext</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Zaměstnané osoby včetně majitelů a spolupracujících osob.</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>převzato (sbs_sc_ovw, EMP_NR)</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Eurostat, sbs_sc_ovw</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>SBS_OBRAT_PODNIK</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Průměrný obrat podniku v ČR podle velikostní třídy (mil. Kč)</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>kontext</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Čistý obrat / počet podniků, převedeno ročním průměrným kurzem CZK/EUR; pásmo min.–max. mezi oddíly sekce.</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>NETTUR_MEUR / ENT_NR × kurz</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Eurostat, sbs_sc_ovw, ert_bil_eur_a</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Peněžní údaje jen za třídy 0–9, 10–19, 20–49, 50–249, 250+.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Průměr, ne medián; fakt za ČR.</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>SBS_MARZE</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Hrubý provozní přebytek / obrat v ČR podle velikostní třídy (%)</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>kontext</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Hrubý provozní přebytek / čistý obrat × 100, za ČR.</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>100 × GOS_MEUR / NETTUR_MEUR</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Eurostat, sbs_sc_ovw</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Fakt za ČR, ne odhad za kraj; hrubý provozní přebytek zahrnuje i odměnu podnikatelů bez zaměstnanců.</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>MODEL_POMER_SBS</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Poměr přidané hodnoty SBS a národních účtů za ČR (týž obor a rok)</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>odhad</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Přidaná hodnota sekce za ČR ze statistiky podniků (SBS, v Kč) / přidaná hodnota téže sekce za ČR z národních (regionálních) účtů.</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AV_MEUR(ČR) × kurz / HPH_CP(ČR)</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>odvozeno z Eurostatu (sbs_sc_ovw, ert_bil_eur_a, nama_10r_3gva)</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Jen jsou-li publikovány obě hodnoty pro týž rok.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Měřítko přepočtu krajské přidané hodnoty pro model (rozhodnutí 14); předpokládá stejný podíl neregistrované ekonomiky v kraji jako v ČR.</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>SBS_HPH</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Přidaná hodnota sekce za ČR podle statistiky podniků (mil. Kč)</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>kontext</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Přidaná hodnota v nákladech na výrobní činitele (SBS), mil. EUR převedené ročním průměrným kurzem.</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AV_MEUR × kurz</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Eurostat, sbs_sc_ovw, ert_bil_eur_a</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Nižší než přidaná hodnota národních účtů (bez neregistrované ekonomiky, jiné ocenění).</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
         <is>
           <t>Pravidla ochrany malých buněk: buňky pod prahem se v každém členění slučují do „ostatní“; je-li „ostatní“ pod prahem, přidá se další nejmenší buňka; skryté číslo nesmí jít dopočítat ze součtů ani z jiné tabulky (ověřeno kontrolou dopočtu). Podrobnosti: docs/report_metodika.md.</t>
         </is>
@@ -12392,7 +13629,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12569,7 +13806,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-19T10:22:30+00:00</t>
+          <t>2026-10-19T13:03:02+00:00</t>
         </is>
       </c>
     </row>

--- a/reporty/ukazky/F__CZ051__2026-10-15/priloha.xlsx
+++ b/reporty/ukazky/F__CZ051__2026-10-15/priloha.xlsx
@@ -13806,7 +13806,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-19T13:03:02+00:00</t>
+          <t>2026-10-19T13:14:33+00:00</t>
         </is>
       </c>
     </row>
